--- a/fod/FOD_Guard_BOM.xlsx
+++ b/fod/FOD_Guard_BOM.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BOM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Central" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -87,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,6 +165,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1476,4 +1502,732 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Central option — one computer, many machines</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>One PC on the plant network runs FOD Guard for every cell; each machine keeps only camera + light + lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Number of machines (edit)</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Head-end (once per plant)</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>Unit (Rs.)</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>Total (Rs.)</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Mini PC, refurbished i5 / 8 GB / 256 GB SSD</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Runs FOD Guard for all cells (browser kiosk)</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E8" s="37">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>24-inch monitor</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Supervision point display</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E9" s="37">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Keyboard + mouse</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>700</v>
+      </c>
+      <c r="E10" s="37">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>8-port Gigabit PoE switch</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Powers all cell cameras over their Cat6 runs</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E11" s="37">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>8 PoE ports = up to 8 cameras; add a switch per 8 cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>UPS 600 VA</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>PC + switch ride-through during changeovers</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="37">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Cat6 drum 100 m + keystones/patch</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Home runs from cells to the switch</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E13" s="37">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Size to your floor layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Head-end subtotal</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="n"/>
+      <c r="E14" s="38">
+        <f>SUM(E8:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Per-machine kit (x number of machines)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Unit (Rs.)</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>Total (Rs.)</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>IP bullet camera 2 MP, fixed 4 mm, PoE</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>JPEG snapshot URL, powered by the PoE switch</t>
+        </is>
+      </c>
+      <c r="C18" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D18" s="36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E18" s="37">
+        <f>C18*D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Camera mounting arm, articulated + clamp</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Rigid mount over the die</t>
+        </is>
+      </c>
+      <c r="C19" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D19" s="36" t="n">
+        <v>600</v>
+      </c>
+      <c r="E19" s="37">
+        <f>C19*D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>LED floodlight 20 W, 4000 K</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Constant die illumination</t>
+        </is>
+      </c>
+      <c r="C20" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D20" s="36" t="n">
+        <v>700</v>
+      </c>
+      <c r="E20" s="37">
+        <f>C20*D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Floodlight bracket + glare hood</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>300</v>
+      </c>
+      <c r="E21" s="37">
+        <f>C21*D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>ESP32 DevKit V1</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Wi-Fi relay node: /lock and /unlock endpoints</t>
+        </is>
+      </c>
+      <c r="C22" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>450</v>
+      </c>
+      <c r="E22" s="37">
+        <f>C22*D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Shelly 1 swap: Rs.1,600, no coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Relay module 2-ch 5 V, opto-isolated</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" s="37">
+        <f>C23*D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>DC-DC buck 12 V to 5 V 3 A</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D24" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="37">
+        <f>C24*D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Solenoid bolt lock 12 V DC</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Guard-door bolt, spring-return</t>
+        </is>
+      </c>
+      <c r="C25" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D25" s="36" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E25" s="37">
+        <f>C25*D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>SMPS 12 V 5 A</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Lock + light supply at the cell</t>
+        </is>
+      </c>
+      <c r="C26" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D26" s="36" t="n">
+        <v>550</v>
+      </c>
+      <c r="E26" s="37">
+        <f>C26*D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Tower light 12 V, 3-colour + buzzer</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Verdict visible at the machine</t>
+        </is>
+      </c>
+      <c r="C27" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="37">
+        <f>C27*D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Optional but recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>ABS IP65 enclosure 200x150 + DIN rail</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D28" s="36" t="n">
+        <v>450</v>
+      </c>
+      <c r="E28" s="37">
+        <f>C28*D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Terminal blocks, glands, flyback diode, MOV, wire</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>1 lot</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D29" s="36" t="n">
+        <v>600</v>
+      </c>
+      <c r="E29" s="37">
+        <f>C29*D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Conduit, saddles, fasteners</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>1 lot</t>
+        </is>
+      </c>
+      <c r="C30" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D30" s="36" t="n">
+        <v>400</v>
+      </c>
+      <c r="E30" s="37">
+        <f>C30*D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Cat6 lead / termination at the cell</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="39">
+        <f>$B$4</f>
+        <v/>
+      </c>
+      <c r="D31" s="36" t="n">
+        <v>250</v>
+      </c>
+      <c r="E31" s="37">
+        <f>C31*D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Per-machine kits subtotal</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="n"/>
+      <c r="E32" s="38">
+        <f>SUM(E18:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="32" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="n"/>
+      <c r="B33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Base total</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="n"/>
+      <c r="E34" s="38">
+        <f>E14+E32</f>
+        <v/>
+      </c>
+      <c r="F34" s="32" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Contingency 10%</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="n"/>
+      <c r="E35" s="37">
+        <f>E34*0.1</f>
+        <v/>
+      </c>
+      <c r="F35" s="32" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (central)</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="n"/>
+      <c r="E36" s="38">
+        <f>E34+E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="32" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Compare: same number of standalone cells (Summary grand total x machines)</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="n"/>
+      <c r="E37" s="37">
+        <f>Summary!B11*B4</f>
+        <v/>
+      </c>
+      <c r="F37" s="32" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="n"/>
+      <c r="B38" s="32" t="n"/>
+      <c r="F38" s="32" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>In the app: give each machine's job its camera snapshot URL and lock/unlock relay URLs (Central-mode fields in the job editor), then use CHECK ALL MACHINES.</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Serve fod/index.html from the central PC (e.g. python -m http.server); pick cameras/DVRs whose snapshot endpoint allows CORS, or run a small snapshot proxy on the PC.</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="n"/>
+      <c r="F40" s="32" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Relay nodes join the plant Wi-Fi (ESP32/Shelly); cameras are powered by the PoE switch, so cells need no per-camera injector.</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>SAFETY: process-assist only — each machine's certified guard interlock stays in place.</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>